--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXV/LTAIPT_A63F35A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXV/LTAIPT_A63F35A.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9C4A9B-81AD-40F4-8D98-07CA1DC86A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -25,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="122">
   <si>
     <t>48996</t>
   </si>
@@ -174,9 +180,6 @@
     <t>436735</t>
   </si>
   <si>
-    <t>436719</t>
-  </si>
-  <si>
     <t>436732</t>
   </si>
   <si>
@@ -234,7 +237,7 @@
     <t>Acciones realizadas por el sujeto obligado para dar cumplimiento a cada uno de los puntos</t>
   </si>
   <si>
-    <t>Dependencias y Entidades Federativas que colaboraron para cumplir con la recomendación, en su caso</t>
+    <t>Dependencias y entidades federativas que hayan colaborado para dar cumplimiento a la Recomendación, en su caso</t>
   </si>
   <si>
     <t>Fecha de notificación a la CNDH o al organismo estatal</t>
@@ -249,7 +252,7 @@
     <t>Fecha de comparecencia, en su caso  (Recomendación no aceptada)</t>
   </si>
   <si>
-    <t>Servidor(es) Público(s) encargado(s) de comparecer  
+    <t>Personas servidoras públicas encargadas de comparecer  
 Tabla_436729</t>
   </si>
   <si>
@@ -274,7 +277,7 @@
     <t>Número de oficio que notifica la respuesta al organismo</t>
   </si>
   <si>
-    <t>Número de denuncia ante el Ministerio Público</t>
+    <t xml:space="preserve">Número de denuncia o en su caso, número de carpeta de investigación </t>
   </si>
   <si>
     <t>Estado de las recomendaciones aceptadas (catálogo)</t>
@@ -286,46 +289,43 @@
     <t>Fecha de notificación de la conclusión, en su caso</t>
   </si>
   <si>
-    <t>Hipervínculo a la versión publica del sistema correspondiente</t>
+    <t>Hipervínculo a la versión pública del Sistema de Seguimiento a Recomendaciones emitidas por la CNDH (SISER) y/o sistemas homólogos</t>
   </si>
   <si>
     <t>Área(s) responsable(s) que genera(n), posee(n), publica(n) y actualizan la información</t>
   </si>
   <si>
-    <t>Fecha de validación</t>
-  </si>
-  <si>
     <t>Fecha de actualización</t>
   </si>
   <si>
     <t>Nota</t>
   </si>
   <si>
-    <t>2023</t>
+    <t>2024</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>subdirección juridica</t>
-  </si>
-  <si>
-    <t>2AA3D40CA1AB5E14405724E8904A16F0</t>
-  </si>
-  <si>
-    <t>01/04/2023</t>
-  </si>
-  <si>
-    <t>30/06/2023</t>
-  </si>
-  <si>
-    <t>8101388</t>
-  </si>
-  <si>
-    <t>26/07/2023</t>
-  </si>
-  <si>
-    <t>Del periodo del 01 de abril de 2023 al 30 de junio de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no generó hipervínculo, toda vez que no hay una recomendación emitida por la Comisión Nacional de Derechos Humanos; tal como lo establece el mismo reglamento interior de la comision nacional en su capitulo VI.  fracciones I, II, III, IV, V, VI, VII, VIII, IX. en el que hace mencion de las causas de conclusion .</t>
+    <t>Subdirección Jurídica</t>
+  </si>
+  <si>
+    <t>220F5A6BCAF3D5F474233CDB580DA90E</t>
+  </si>
+  <si>
+    <t>01/04/2024</t>
+  </si>
+  <si>
+    <t>30/06/2024</t>
+  </si>
+  <si>
+    <t>14422821</t>
+  </si>
+  <si>
+    <t>04/07/2024</t>
+  </si>
+  <si>
+    <t>Del periodo del 01 de abril de 2024 al 30 de junio de 2024, el Colegio de Bachilleres del Estado de Tlaxcala no generó hipervínculo, toda vez que no hay una recomendación emitida por la Comisión Nacional de Derechos Humanos; tal como lo establece el mismo reglamento interior de la comision nacional en su capitulo VI.  fracciones I, II, III, IV, V, VI, VII, VIII, IX. en el que hace mencion de las causas de conclusion .</t>
   </si>
   <si>
     <t>Recomendación específica</t>
@@ -403,7 +403,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -502,6 +502,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -517,44 +520,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -582,14 +585,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -617,6 +637,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -628,175 +665,151 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AL8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -813,12 +826,12 @@
     <col min="15" max="15" width="46.85546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="55.85546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="77" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="87.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="99.140625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="46.85546875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="53.7109375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="45.140625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="58.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="45.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="49.5703125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="49.28515625" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="36" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="34" bestFit="1" customWidth="1"/>
@@ -826,23 +839,22 @@
     <col min="28" max="28" width="54.85546875" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="46.5703125" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="47.7109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="61.140625" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="45.5703125" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="27.85546875" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="42.7109375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="52.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="115.28515625" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="20" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="255" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="20" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -859,7 +871,7 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -874,7 +886,7 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="1:39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -981,16 +993,13 @@
         <v>10</v>
       </c>
       <c r="AK4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AL4" t="s">
-        <v>12</v>
-      </c>
-      <c r="AM4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>14</v>
       </c>
@@ -1102,13 +1111,10 @@
       <c r="AL5" t="s">
         <v>50</v>
       </c>
-      <c r="AM5" t="s">
+    </row>
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -1147,246 +1153,239 @@
       <c r="AJ6" s="5"/>
       <c r="AK6" s="5"/>
       <c r="AL6" s="5"/>
-      <c r="AM6" s="5"/>
-    </row>
-    <row r="7" spans="1:39" ht="26.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:38" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="U7" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="V7" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="W7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="X7" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="X7" s="2" t="s">
+      <c r="Y7" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="Y7" s="2" t="s">
+      <c r="Z7" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="Z7" s="2" t="s">
+      <c r="AA7" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="AA7" s="2" t="s">
+      <c r="AB7" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="AB7" s="2" t="s">
+      <c r="AC7" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="AC7" s="2" t="s">
+      <c r="AD7" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="AD7" s="2" t="s">
+      <c r="AE7" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="AE7" s="2" t="s">
+      <c r="AF7" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="AF7" s="2" t="s">
+      <c r="AG7" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="AG7" s="2" t="s">
+      <c r="AH7" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="AH7" s="2" t="s">
+      <c r="AI7" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AI7" s="2" t="s">
+      <c r="AJ7" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AJ7" s="2" t="s">
+      <c r="AK7" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="AK7" s="2" t="s">
+      <c r="AL7" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="AL7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:38" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="AM7" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:39" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="C8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AG8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AI8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ8" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="AK8" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="W8" s="3" t="s">
+      <c r="AL8" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="X8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="AE8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="AF8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="AG8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="AH8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="AI8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="AJ8" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="AK8" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="AL8" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="AM8" s="3" t="s">
-        <v>99</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:AM6"/>
+    <mergeCell ref="A6:AL6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -1395,13 +1394,13 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H8:H200">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H8:H199" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Hidden_17</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L8:L200">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L8:L199" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>Hidden_211</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AF8:AF200">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AF8:AF199" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>Hidden_331</formula1>
     </dataValidation>
   </dataValidations>
@@ -1410,28 +1409,28 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1440,18 +1439,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1460,43 +1459,43 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1505,7 +1504,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1531,39 +1530,39 @@
     </row>
     <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E2" t="s">
         <v>113</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>114</v>
-      </c>
-      <c r="E2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F2" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>121</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F4:F201">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F4:F201" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>Hidden_1_Tabla_4367295</formula1>
     </dataValidation>
   </dataValidations>
@@ -1572,18 +1571,18 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXV/LTAIPT_A63F35A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXV/LTAIPT_A63F35A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\TERCER TRIMESTRE JULIO-SEPTIEMBRE 2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9C4A9B-81AD-40F4-8D98-07CA1DC86A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51D8FCD2-D132-4631-B8E6-3AF351F79E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -301,31 +301,31 @@
     <t>Nota</t>
   </si>
   <si>
+    <t>91B8199821A44B1FC2D682BB66AAE2F7</t>
+  </si>
+  <si>
     <t>2024</t>
   </si>
   <si>
+    <t>01/07/2024</t>
+  </si>
+  <si>
+    <t>30/09/2024</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
+    <t>15970615</t>
+  </si>
+  <si>
     <t>Subdirección Jurídica</t>
   </si>
   <si>
-    <t>220F5A6BCAF3D5F474233CDB580DA90E</t>
-  </si>
-  <si>
-    <t>01/04/2024</t>
-  </si>
-  <si>
-    <t>30/06/2024</t>
-  </si>
-  <si>
-    <t>14422821</t>
-  </si>
-  <si>
-    <t>04/07/2024</t>
-  </si>
-  <si>
-    <t>Del periodo del 01 de abril de 2024 al 30 de junio de 2024, el Colegio de Bachilleres del Estado de Tlaxcala no generó hipervínculo, toda vez que no hay una recomendación emitida por la Comisión Nacional de Derechos Humanos; tal como lo establece el mismo reglamento interior de la comision nacional en su capitulo VI.  fracciones I, II, III, IV, V, VI, VII, VIII, IX. en el que hace mencion de las causas de conclusion .</t>
+    <t>03/10/2024</t>
+  </si>
+  <si>
+    <t>Del periodo del 01 de julio de 2024 al 30 de septiembre de 2024, el Colegio de Bachilleres del Estado de Tlaxcala no generó hipervínculo, toda vez que no hay una recomendación emitida por la Comisión Nacional de Derechos Humanos; tal como lo establece el mismo reglamento interior de la comision nacional en su capitulo VI.  fracciones I, II, III, IV, V, VI, VII, VIII, IX. en el que hace mencion de las causas de conclusion .</t>
   </si>
   <si>
     <t>Recomendación específica</t>
@@ -1269,112 +1269,112 @@
     </row>
     <row r="8" spans="1:38" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="W8" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="W8" s="3" t="s">
+      <c r="X8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AB8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AD8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AF8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AH8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AJ8" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="X8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="Y8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AA8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AC8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AD8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AE8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AF8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AG8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AH8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AI8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AJ8" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="AK8" s="3" t="s">
         <v>96</v>
